--- a/data/CL31.xlsx
+++ b/data/CL31.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adane\dm_tracker\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E9076B-3F3B-4992-8B5E-1B72D4CB9A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B4CA55-77A0-48E5-816A-7ACC1EA4DB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7BD6478B-385B-46E3-99A0-A28036FEB319}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="206">
   <si>
     <t>Activity Name</t>
   </si>
@@ -68,16 +68,10 @@
     <t>Contract Completion CC 19th July</t>
   </si>
   <si>
-    <t>20-Jul-26*</t>
-  </si>
-  <si>
     <t>Mandatory Finish</t>
   </si>
   <si>
     <t>ECI Contract award</t>
-  </si>
-  <si>
-    <t>15-Dec-25*</t>
   </si>
   <si>
     <t>Start On</t>
@@ -1099,8 +1093,8 @@
         <v>0</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
+      <c r="D2" s="2">
+        <v>46223</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="2">
@@ -1113,18 +1107,18 @@
         <v>0</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
+      <c r="C3" s="2">
+        <v>46006</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="2">
@@ -1138,12 +1132,12 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
         <v>0</v>
@@ -1166,7 +1160,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
         <v>10</v>
@@ -1193,13 +1187,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="2">
@@ -1213,12 +1207,12 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1">
         <v>10</v>
@@ -1245,7 +1239,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1">
         <v>0</v>
@@ -1268,7 +1262,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1">
         <v>0</v>
@@ -1291,7 +1285,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" s="1">
         <v>8</v>
@@ -1309,12 +1303,12 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
@@ -1332,12 +1326,12 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1">
         <v>0</v>
@@ -1353,12 +1347,12 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1">
         <v>8</v>
@@ -1376,12 +1370,12 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1">
         <v>8</v>
@@ -1399,12 +1393,12 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B15" s="1">
         <v>5</v>
@@ -1422,12 +1416,12 @@
         <v>0</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1">
         <v>5</v>
@@ -1445,12 +1439,12 @@
         <v>0</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B17" s="1">
         <v>10</v>
@@ -1468,12 +1462,12 @@
         <v>0</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" s="1">
         <v>5</v>
@@ -1491,12 +1485,12 @@
         <v>0</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B19" s="1">
         <v>5</v>
@@ -1514,12 +1508,12 @@
         <v>0</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B20" s="1">
         <v>5</v>
@@ -1537,12 +1531,12 @@
         <v>0</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B21" s="1">
         <v>35</v>
@@ -1560,12 +1554,12 @@
         <v>0</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1">
         <v>8</v>
@@ -1583,12 +1577,12 @@
         <v>0</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1">
         <v>35</v>
@@ -1606,12 +1600,12 @@
         <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B24" s="1">
         <v>5</v>
@@ -1629,12 +1623,12 @@
         <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B25" s="1">
         <v>15</v>
@@ -1652,12 +1646,12 @@
         <v>0</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B26" s="1">
         <v>15</v>
@@ -1675,12 +1669,12 @@
         <v>0</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B27" s="1">
         <v>10</v>
@@ -1698,12 +1692,12 @@
         <v>0</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B28" s="1">
         <v>10</v>
@@ -1721,12 +1715,12 @@
         <v>0</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B29" s="1">
         <v>5</v>
@@ -1744,12 +1738,12 @@
         <v>0</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B30" s="1">
         <v>5</v>
@@ -1767,12 +1761,12 @@
         <v>0</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B31" s="1">
         <v>15</v>
@@ -1790,12 +1784,12 @@
         <v>0</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B32" s="1">
         <v>1</v>
@@ -1813,12 +1807,12 @@
         <v>0</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B33" s="1">
         <v>0</v>
@@ -1841,7 +1835,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B34" s="1">
         <v>0</v>
@@ -1865,12 +1859,12 @@
         <v>7</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B35" s="1">
         <v>10</v>
@@ -1894,12 +1888,12 @@
         <v>7</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B36" s="1">
         <v>30</v>
@@ -1923,12 +1917,12 @@
         <v>0</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B37" s="1">
         <v>20</v>
@@ -1952,12 +1946,12 @@
         <v>0</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B38" s="1">
         <v>10</v>
@@ -1984,7 +1978,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B39" s="1">
         <v>15</v>
@@ -2011,7 +2005,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B40" s="1">
         <v>30</v>
@@ -2038,7 +2032,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B41" s="1">
         <v>15</v>
@@ -2065,7 +2059,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B42" s="1">
         <v>1</v>
@@ -2092,7 +2086,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B43" s="1">
         <v>1</v>
@@ -2119,7 +2113,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B44" s="1">
         <v>0</v>
@@ -2138,7 +2132,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B45" s="1">
         <v>35</v>
@@ -2165,7 +2159,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B46" s="1">
         <v>15</v>
@@ -2192,7 +2186,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B47" s="1">
         <v>70</v>
@@ -2219,7 +2213,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B48" s="1">
         <v>25</v>
@@ -2246,7 +2240,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B49" s="1">
         <v>10</v>
@@ -2273,7 +2267,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B50" s="1">
         <v>5</v>
@@ -2300,7 +2294,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B51" s="1">
         <v>60</v>
@@ -2327,7 +2321,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B52" s="1">
         <v>50</v>
@@ -2354,7 +2348,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B53" s="1">
         <v>5</v>
@@ -2381,7 +2375,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B54" s="1">
         <v>10</v>
@@ -2408,7 +2402,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B55" s="1">
         <v>6</v>
@@ -2435,7 +2429,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B56" s="1">
         <v>0</v>
@@ -2455,12 +2449,12 @@
         <v>7</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B57" s="1">
         <v>0</v>
@@ -2480,12 +2474,12 @@
         <v>7</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B58" s="1">
         <v>0</v>
@@ -2505,12 +2499,12 @@
         <v>7</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B59" s="1">
         <v>0</v>
@@ -2530,12 +2524,12 @@
         <v>7</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B60" s="1">
         <v>0</v>
@@ -2555,12 +2549,12 @@
         <v>7</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B61" s="1">
         <v>0</v>
@@ -2580,12 +2574,12 @@
         <v>7</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B62" s="1">
         <v>0</v>
@@ -2605,12 +2599,12 @@
         <v>7</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B63" s="1">
         <v>0</v>
@@ -2630,12 +2624,12 @@
         <v>7</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B64" s="1">
         <v>0</v>
@@ -2655,12 +2649,12 @@
         <v>7</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B65" s="1">
         <v>30</v>
@@ -2684,12 +2678,12 @@
         <v>9</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B66" s="1">
         <v>5</v>
@@ -2716,7 +2710,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B67" s="1">
         <v>11</v>
@@ -2743,7 +2737,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B68" s="1">
         <v>0</v>
@@ -2766,7 +2760,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B69" s="1">
         <v>0</v>
@@ -2789,7 +2783,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B70" s="1">
         <v>0</v>
@@ -2812,7 +2806,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B71" s="1">
         <v>6</v>
@@ -2839,7 +2833,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B72" s="1">
         <v>0</v>
@@ -2862,7 +2856,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B73" s="1">
         <v>6</v>
@@ -2889,7 +2883,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B74" s="1">
         <v>0</v>
@@ -2912,7 +2906,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B75" s="1">
         <v>0</v>
@@ -2935,7 +2929,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B76" s="1">
         <v>0</v>
@@ -2958,7 +2952,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B77" s="1">
         <v>0</v>
@@ -2981,7 +2975,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B78" s="1">
         <v>0</v>
@@ -3004,7 +2998,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B79" s="1">
         <v>0</v>
@@ -3027,7 +3021,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B80" s="1">
         <v>0</v>
@@ -3050,7 +3044,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B81" s="1">
         <v>0</v>
@@ -3073,7 +3067,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B82" s="1">
         <v>0</v>
@@ -3096,7 +3090,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B83" s="1">
         <v>6</v>
@@ -3123,7 +3117,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B84" s="1">
         <v>10</v>
@@ -3150,7 +3144,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B85" s="1">
         <v>6</v>
@@ -3177,7 +3171,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B86" s="1">
         <v>6</v>
@@ -3204,7 +3198,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B87" s="1">
         <v>6</v>
@@ -3231,7 +3225,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B88" s="1">
         <v>22</v>
@@ -3258,7 +3252,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B89" s="1">
         <v>6</v>
@@ -3285,7 +3279,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B90" s="1">
         <v>6</v>
@@ -3312,7 +3306,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B91" s="1">
         <v>6</v>
@@ -3339,7 +3333,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B92" s="1">
         <v>6</v>
@@ -3366,7 +3360,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B93" s="1">
         <v>4</v>
@@ -3393,7 +3387,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B94" s="1">
         <v>6</v>
@@ -3420,7 +3414,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B95" s="1">
         <v>6</v>
@@ -3447,7 +3441,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B96" s="1">
         <v>6</v>
@@ -3474,7 +3468,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B97" s="1">
         <v>11</v>
@@ -3501,7 +3495,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B98" s="1">
         <v>6</v>
@@ -3528,7 +3522,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B99" s="1">
         <v>11</v>
@@ -3555,7 +3549,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B100" s="1">
         <v>6</v>
@@ -3582,7 +3576,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B101" s="1">
         <v>2</v>
@@ -3609,7 +3603,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B102" s="1">
         <v>6</v>
@@ -3636,7 +3630,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B103" s="1">
         <v>3</v>
@@ -3663,7 +3657,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B104" s="1">
         <v>11</v>
@@ -3690,7 +3684,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B105" s="1">
         <v>11</v>
@@ -3717,7 +3711,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B106" s="1">
         <v>6</v>
@@ -3744,7 +3738,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B107" s="1">
         <v>6</v>
@@ -3771,7 +3765,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B108" s="1">
         <v>6</v>
@@ -3798,7 +3792,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B109" s="1">
         <v>6</v>
@@ -3825,7 +3819,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B110" s="1">
         <v>6</v>
@@ -3852,7 +3846,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B111" s="1">
         <v>6</v>
@@ -3879,7 +3873,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B112" s="1">
         <v>6</v>
@@ -3906,7 +3900,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B113" s="1">
         <v>4</v>
@@ -3933,7 +3927,7 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B114" s="1">
         <v>4</v>
@@ -3960,7 +3954,7 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B115" s="1">
         <v>4</v>
@@ -3987,7 +3981,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B116" s="1">
         <v>4</v>
@@ -4014,7 +4008,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B117" s="1">
         <v>4</v>
@@ -4041,7 +4035,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B118" s="1">
         <v>11</v>
@@ -4068,7 +4062,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B119" s="1">
         <v>11</v>
@@ -4095,7 +4089,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B120" s="1">
         <v>6</v>
@@ -4122,7 +4116,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B121" s="1">
         <v>4</v>
@@ -4149,7 +4143,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B122" s="1">
         <v>6</v>
@@ -4176,7 +4170,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B123" s="1">
         <v>11</v>
@@ -4203,7 +4197,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B124" s="1">
         <v>4</v>
@@ -4230,7 +4224,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B125" s="1">
         <v>11</v>
@@ -4257,7 +4251,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B126" s="1">
         <v>6</v>
@@ -4284,7 +4278,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B127" s="1">
         <v>6</v>
@@ -4311,7 +4305,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B128" s="1">
         <v>6</v>
@@ -4338,7 +4332,7 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B129" s="1">
         <v>11</v>
@@ -4365,7 +4359,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B130" s="1">
         <v>0</v>
@@ -4388,7 +4382,7 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B131" s="1">
         <v>11</v>
@@ -4415,7 +4409,7 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B132" s="1">
         <v>0</v>
@@ -4442,7 +4436,7 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B133" s="1">
         <v>22</v>
@@ -4469,7 +4463,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B134" s="1">
         <v>17</v>
@@ -4496,7 +4490,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B135" s="1">
         <v>5</v>
@@ -4523,7 +4517,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B136" s="1">
         <v>44</v>
@@ -4550,7 +4544,7 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B137" s="1">
         <v>22</v>
@@ -4577,7 +4571,7 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B138" s="1">
         <v>6</v>
@@ -4604,7 +4598,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B139" s="1">
         <v>6</v>
@@ -4631,7 +4625,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B140" s="1">
         <v>5</v>
@@ -4658,7 +4652,7 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B141" s="1">
         <v>11</v>
@@ -4685,7 +4679,7 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B142" s="1">
         <v>11</v>
@@ -4712,7 +4706,7 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B143" s="1">
         <v>5</v>
@@ -4739,7 +4733,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B144" s="1">
         <v>22</v>
@@ -4766,7 +4760,7 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B145" s="1">
         <v>5</v>
@@ -4793,7 +4787,7 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B146" s="1">
         <v>10</v>
@@ -4820,7 +4814,7 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B147" s="1">
         <v>11</v>
@@ -4847,7 +4841,7 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B148" s="1">
         <v>5</v>
@@ -4874,7 +4868,7 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B149" s="1">
         <v>28</v>
@@ -4901,7 +4895,7 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B150" s="1">
         <v>5</v>
@@ -4928,7 +4922,7 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B151" s="1">
         <v>28</v>
@@ -4955,7 +4949,7 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B152" s="1">
         <v>20</v>
@@ -4982,7 +4976,7 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B153" s="1">
         <v>0</v>
@@ -5005,7 +4999,7 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B154" s="1">
         <v>0</v>
@@ -5028,7 +5022,7 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B155" s="1">
         <v>6</v>
@@ -5055,7 +5049,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B156" s="1">
         <v>30</v>
@@ -5082,7 +5076,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B157" s="1">
         <v>10</v>
@@ -5109,7 +5103,7 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B158" s="1">
         <v>6</v>
@@ -5136,7 +5130,7 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B159" s="1">
         <v>6</v>
@@ -5163,7 +5157,7 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B160" s="1">
         <v>6</v>
@@ -5190,7 +5184,7 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B161" s="1">
         <v>17</v>
@@ -5217,7 +5211,7 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B162" s="1">
         <v>2</v>
@@ -5244,7 +5238,7 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B163" s="1">
         <v>0</v>
@@ -5267,7 +5261,7 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B164" s="1">
         <v>0</v>
@@ -5290,7 +5284,7 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B165" s="1">
         <v>0</v>
@@ -5313,7 +5307,7 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B166" s="1">
         <v>0</v>
@@ -5336,7 +5330,7 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B167" s="1">
         <v>0</v>
@@ -5359,7 +5353,7 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B168" s="1">
         <v>5</v>
@@ -5386,7 +5380,7 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B169" s="1">
         <v>5</v>
@@ -5413,7 +5407,7 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B170" s="1">
         <v>5</v>
@@ -5440,7 +5434,7 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B171" s="1">
         <v>5</v>
@@ -5467,7 +5461,7 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B172" s="1">
         <v>5</v>
@@ -5494,7 +5488,7 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B173" s="1">
         <v>1</v>
@@ -5521,7 +5515,7 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B174" s="1">
         <v>5</v>
@@ -5548,7 +5542,7 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B175" s="1">
         <v>4</v>
@@ -5575,7 +5569,7 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B176" s="1">
         <v>2</v>
@@ -5602,7 +5596,7 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B177" s="1">
         <v>2</v>
@@ -5629,7 +5623,7 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B178" s="1">
         <v>2</v>
@@ -5656,7 +5650,7 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B179" s="1">
         <v>5</v>
@@ -5683,7 +5677,7 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B180" s="1">
         <v>20</v>
@@ -5710,7 +5704,7 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B181" s="1">
         <v>6</v>
@@ -5737,7 +5731,7 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B182" s="1">
         <v>5</v>
@@ -5764,7 +5758,7 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B183" s="1">
         <v>1</v>
@@ -5791,7 +5785,7 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B184" s="1">
         <v>6</v>
@@ -5818,7 +5812,7 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B185" s="1">
         <v>3</v>
@@ -5845,7 +5839,7 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B186" s="1">
         <v>3</v>
@@ -5872,7 +5866,7 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B187" s="1">
         <v>3</v>
@@ -5899,7 +5893,7 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B188" s="1">
         <v>4</v>
@@ -5926,7 +5920,7 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B189" s="1">
         <v>11</v>
@@ -5953,7 +5947,7 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B190" s="1">
         <v>4</v>
@@ -5980,7 +5974,7 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B191" s="1">
         <v>14</v>
@@ -6007,7 +6001,7 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B192" s="1">
         <v>5</v>
@@ -6034,7 +6028,7 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B193" s="1">
         <v>20</v>
@@ -6061,7 +6055,7 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B194" s="1">
         <v>2</v>
@@ -6088,7 +6082,7 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B195" s="1">
         <v>3</v>
@@ -6115,7 +6109,7 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B196" s="1">
         <v>10</v>

--- a/data/CL31.xlsx
+++ b/data/CL31.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adane\dm_tracker\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A2156D4-51F0-41B3-B4DE-7C2435FDC580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8906824D-A6D3-4D93-A329-E83E370578E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7BD6478B-385B-46E3-99A0-A28036FEB319}"/>
   </bookViews>
@@ -68,9 +68,6 @@
     <t>Primary Constraint</t>
   </si>
   <si>
-    <t>Ferry PS - Advanced Implementation Work  - CL31- 27-02-26  - Accepted</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Key Dates</t>
   </si>
   <si>
@@ -1668,6 +1665,9 @@
   </si>
   <si>
     <t xml:space="preserve">    Close-Out (R)</t>
+  </si>
+  <si>
+    <t>FPS - Advanced Implementation Work  - CL31- 27-02-26  - Accepted</t>
   </si>
 </sst>
 </file>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>543</v>
       </c>
       <c r="C2">
         <v>141</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>141</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
         <v>13</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
       </c>
       <c r="G4" s="1">
         <v>46223</v>
@@ -2155,21 +2155,21 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
         <v>17</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
       </c>
       <c r="F5" s="1">
         <v>46006</v>
@@ -2181,15 +2181,15 @@
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
         <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
         <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -2238,16 +2238,16 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
         <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
       </c>
       <c r="F8" s="1">
         <v>46029</v>
@@ -2259,15 +2259,15 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
         <v>27</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -2293,7 +2293,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10">
         <v>102</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -2330,7 +2330,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12">
         <v>102</v>
@@ -2356,10 +2356,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" t="s">
         <v>32</v>
-      </c>
-      <c r="B13" t="s">
-        <v>33</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
         <v>34</v>
-      </c>
-      <c r="B14" t="s">
-        <v>35</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15">
         <v>60</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -2441,7 +2441,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18">
         <v>60</v>
@@ -2458,10 +2458,10 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
         <v>40</v>
-      </c>
-      <c r="B19" t="s">
-        <v>41</v>
       </c>
       <c r="C19">
         <v>8</v>
@@ -2476,15 +2476,15 @@
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" t="s">
         <v>43</v>
-      </c>
-      <c r="B20" t="s">
-        <v>44</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -2499,15 +2499,15 @@
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
         <v>45</v>
-      </c>
-      <c r="B21" t="s">
-        <v>46</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2519,15 +2519,15 @@
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s">
         <v>47</v>
-      </c>
-      <c r="B22" t="s">
-        <v>48</v>
       </c>
       <c r="C22">
         <v>8</v>
@@ -2542,15 +2542,15 @@
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" t="s">
         <v>49</v>
-      </c>
-      <c r="B23" t="s">
-        <v>50</v>
       </c>
       <c r="C23">
         <v>8</v>
@@ -2565,12 +2565,12 @@
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C24">
         <v>51</v>
@@ -2587,10 +2587,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" t="s">
         <v>52</v>
-      </c>
-      <c r="B25" t="s">
-        <v>53</v>
       </c>
       <c r="C25">
         <v>5</v>
@@ -2605,15 +2605,15 @@
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" t="s">
         <v>54</v>
-      </c>
-      <c r="B26" t="s">
-        <v>55</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -2628,15 +2628,15 @@
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" t="s">
         <v>56</v>
-      </c>
-      <c r="B27" t="s">
-        <v>57</v>
       </c>
       <c r="C27">
         <v>10</v>
@@ -2651,15 +2651,15 @@
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" t="s">
         <v>58</v>
-      </c>
-      <c r="B28" t="s">
-        <v>59</v>
       </c>
       <c r="C28">
         <v>5</v>
@@ -2674,15 +2674,15 @@
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" t="s">
         <v>60</v>
-      </c>
-      <c r="B29" t="s">
-        <v>61</v>
       </c>
       <c r="C29">
         <v>5</v>
@@ -2697,15 +2697,15 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" t="s">
         <v>62</v>
-      </c>
-      <c r="B30" t="s">
-        <v>63</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -2720,15 +2720,15 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" t="s">
         <v>64</v>
-      </c>
-      <c r="B31" t="s">
-        <v>65</v>
       </c>
       <c r="C31">
         <v>35</v>
@@ -2743,15 +2743,15 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" t="s">
         <v>66</v>
-      </c>
-      <c r="B32" t="s">
-        <v>67</v>
       </c>
       <c r="C32">
         <v>8</v>
@@ -2766,15 +2766,15 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>67</v>
+      </c>
+      <c r="B33" t="s">
         <v>68</v>
-      </c>
-      <c r="B33" t="s">
-        <v>69</v>
       </c>
       <c r="C33">
         <v>35</v>
@@ -2789,15 +2789,15 @@
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" t="s">
         <v>70</v>
-      </c>
-      <c r="B34" t="s">
-        <v>71</v>
       </c>
       <c r="C34">
         <v>5</v>
@@ -2812,15 +2812,15 @@
         <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>71</v>
+      </c>
+      <c r="B35" t="s">
         <v>72</v>
-      </c>
-      <c r="B35" t="s">
-        <v>73</v>
       </c>
       <c r="C35">
         <v>15</v>
@@ -2835,15 +2835,15 @@
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" t="s">
         <v>74</v>
-      </c>
-      <c r="B36" t="s">
-        <v>75</v>
       </c>
       <c r="C36">
         <v>15</v>
@@ -2858,15 +2858,15 @@
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" t="s">
         <v>76</v>
-      </c>
-      <c r="B37" t="s">
-        <v>77</v>
       </c>
       <c r="C37">
         <v>10</v>
@@ -2881,15 +2881,15 @@
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" t="s">
         <v>78</v>
-      </c>
-      <c r="B38" t="s">
-        <v>79</v>
       </c>
       <c r="C38">
         <v>10</v>
@@ -2904,15 +2904,15 @@
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" t="s">
         <v>80</v>
-      </c>
-      <c r="B39" t="s">
-        <v>81</v>
       </c>
       <c r="C39">
         <v>5</v>
@@ -2927,15 +2927,15 @@
         <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" t="s">
         <v>82</v>
-      </c>
-      <c r="B40" t="s">
-        <v>83</v>
       </c>
       <c r="C40">
         <v>5</v>
@@ -2950,15 +2950,15 @@
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41" t="s">
         <v>84</v>
-      </c>
-      <c r="B41" t="s">
-        <v>85</v>
       </c>
       <c r="C41">
         <v>15</v>
@@ -2973,15 +2973,15 @@
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" t="s">
         <v>86</v>
-      </c>
-      <c r="B42" t="s">
-        <v>87</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -2996,12 +2996,12 @@
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C43">
         <v>95</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>88</v>
+      </c>
+      <c r="B44" t="s">
         <v>89</v>
-      </c>
-      <c r="B44" t="s">
-        <v>90</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -3050,7 +3050,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -3061,7 +3061,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C46">
         <v>10</v>
@@ -3087,10 +3087,10 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" t="s">
         <v>93</v>
-      </c>
-      <c r="B47" t="s">
-        <v>94</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -3114,15 +3114,15 @@
         <v>7</v>
       </c>
       <c r="J47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" t="s">
         <v>95</v>
-      </c>
-      <c r="B48" t="s">
-        <v>96</v>
       </c>
       <c r="C48">
         <v>10</v>
@@ -3146,12 +3146,12 @@
         <v>7</v>
       </c>
       <c r="J48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C49">
         <v>50</v>
@@ -3177,10 +3177,10 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B50" t="s">
         <v>98</v>
-      </c>
-      <c r="B50" t="s">
-        <v>99</v>
       </c>
       <c r="C50">
         <v>30</v>
@@ -3204,15 +3204,15 @@
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" t="s">
         <v>100</v>
-      </c>
-      <c r="B51" t="s">
-        <v>101</v>
       </c>
       <c r="C51">
         <v>20</v>
@@ -3236,12 +3236,12 @@
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C54">
         <v>25</v>
@@ -3289,10 +3289,10 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>104</v>
+      </c>
+      <c r="B55" t="s">
         <v>105</v>
-      </c>
-      <c r="B55" t="s">
-        <v>106</v>
       </c>
       <c r="C55">
         <v>10</v>
@@ -3318,10 +3318,10 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>106</v>
+      </c>
+      <c r="B56" t="s">
         <v>107</v>
-      </c>
-      <c r="B56" t="s">
-        <v>108</v>
       </c>
       <c r="C56">
         <v>15</v>
@@ -3347,7 +3347,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -3358,7 +3358,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C58">
         <v>45</v>
@@ -3384,10 +3384,10 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>110</v>
+      </c>
+      <c r="B59" t="s">
         <v>111</v>
-      </c>
-      <c r="B59" t="s">
-        <v>112</v>
       </c>
       <c r="C59">
         <v>30</v>
@@ -3413,10 +3413,10 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>112</v>
+      </c>
+      <c r="B60" t="s">
         <v>113</v>
-      </c>
-      <c r="B60" t="s">
-        <v>114</v>
       </c>
       <c r="C60">
         <v>15</v>
@@ -3442,7 +3442,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -3468,10 +3468,10 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>115</v>
+      </c>
+      <c r="B62" t="s">
         <v>116</v>
-      </c>
-      <c r="B62" t="s">
-        <v>117</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>117</v>
+      </c>
+      <c r="B63" t="s">
         <v>118</v>
-      </c>
-      <c r="B63" t="s">
-        <v>119</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -3526,7 +3526,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -3537,7 +3537,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -3548,7 +3548,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C67">
         <v>50</v>
@@ -3585,10 +3585,10 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>123</v>
+      </c>
+      <c r="B68" t="s">
         <v>124</v>
-      </c>
-      <c r="B68" t="s">
-        <v>125</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>125</v>
+      </c>
+      <c r="B69" t="s">
         <v>126</v>
-      </c>
-      <c r="B69" t="s">
-        <v>127</v>
       </c>
       <c r="C69">
         <v>35</v>
@@ -3631,10 +3631,10 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>127</v>
+      </c>
+      <c r="B70" t="s">
         <v>128</v>
-      </c>
-      <c r="B70" t="s">
-        <v>129</v>
       </c>
       <c r="C70">
         <v>15</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -3682,7 +3682,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3693,7 +3693,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -3704,7 +3704,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3726,7 +3726,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -3737,7 +3737,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C79">
         <v>95</v>
@@ -3774,10 +3774,10 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>138</v>
+      </c>
+      <c r="B80" t="s">
         <v>139</v>
-      </c>
-      <c r="B80" t="s">
-        <v>140</v>
       </c>
       <c r="C80">
         <v>70</v>
@@ -3803,10 +3803,10 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>140</v>
+      </c>
+      <c r="B81" t="s">
         <v>141</v>
-      </c>
-      <c r="B81" t="s">
-        <v>142</v>
       </c>
       <c r="C81">
         <v>25</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C84">
         <v>76</v>
@@ -3880,7 +3880,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C85">
         <v>15</v>
@@ -3906,10 +3906,10 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>146</v>
+      </c>
+      <c r="B86" t="s">
         <v>147</v>
-      </c>
-      <c r="B86" t="s">
-        <v>148</v>
       </c>
       <c r="C86">
         <v>10</v>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>148</v>
+      </c>
+      <c r="B87" t="s">
         <v>149</v>
-      </c>
-      <c r="B87" t="s">
-        <v>150</v>
       </c>
       <c r="C87">
         <v>5</v>
@@ -3964,7 +3964,7 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C88">
         <v>76</v>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>151</v>
+      </c>
+      <c r="B89" t="s">
         <v>152</v>
-      </c>
-      <c r="B89" t="s">
-        <v>153</v>
       </c>
       <c r="C89">
         <v>60</v>
@@ -4019,10 +4019,10 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>153</v>
+      </c>
+      <c r="B90" t="s">
         <v>154</v>
-      </c>
-      <c r="B90" t="s">
-        <v>155</v>
       </c>
       <c r="C90">
         <v>50</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>155</v>
+      </c>
+      <c r="B91" t="s">
         <v>156</v>
-      </c>
-      <c r="B91" t="s">
-        <v>157</v>
       </c>
       <c r="C91">
         <v>5</v>
@@ -4077,10 +4077,10 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>157</v>
+      </c>
+      <c r="B92" t="s">
         <v>158</v>
-      </c>
-      <c r="B92" t="s">
-        <v>159</v>
       </c>
       <c r="C92">
         <v>10</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>159</v>
+      </c>
+      <c r="B93" t="s">
         <v>160</v>
-      </c>
-      <c r="B93" t="s">
-        <v>161</v>
       </c>
       <c r="C93">
         <v>6</v>
@@ -4135,7 +4135,7 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>162</v>
+      </c>
+      <c r="B95" t="s">
         <v>163</v>
-      </c>
-      <c r="B95" t="s">
-        <v>164</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -4182,15 +4182,15 @@
         <v>7</v>
       </c>
       <c r="J95" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>164</v>
+      </c>
+      <c r="B96" t="s">
         <v>165</v>
-      </c>
-      <c r="B96" t="s">
-        <v>166</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -4208,15 +4208,15 @@
         <v>7</v>
       </c>
       <c r="J96" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>166</v>
+      </c>
+      <c r="B97" t="s">
         <v>167</v>
-      </c>
-      <c r="B97" t="s">
-        <v>168</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -4234,15 +4234,15 @@
         <v>7</v>
       </c>
       <c r="J97" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>168</v>
+      </c>
+      <c r="B98" t="s">
         <v>169</v>
-      </c>
-      <c r="B98" t="s">
-        <v>170</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -4260,15 +4260,15 @@
         <v>7</v>
       </c>
       <c r="J98" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>170</v>
+      </c>
+      <c r="B99" t="s">
         <v>171</v>
-      </c>
-      <c r="B99" t="s">
-        <v>172</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -4286,15 +4286,15 @@
         <v>7</v>
       </c>
       <c r="J99" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>172</v>
+      </c>
+      <c r="B100" t="s">
         <v>173</v>
-      </c>
-      <c r="B100" t="s">
-        <v>174</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -4312,15 +4312,15 @@
         <v>7</v>
       </c>
       <c r="J100" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>174</v>
+      </c>
+      <c r="B101" t="s">
         <v>175</v>
-      </c>
-      <c r="B101" t="s">
-        <v>176</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -4338,15 +4338,15 @@
         <v>7</v>
       </c>
       <c r="J101" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>176</v>
+      </c>
+      <c r="B102" t="s">
         <v>177</v>
-      </c>
-      <c r="B102" t="s">
-        <v>178</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -4364,15 +4364,15 @@
         <v>7</v>
       </c>
       <c r="J102" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>178</v>
+      </c>
+      <c r="B103" t="s">
         <v>179</v>
-      </c>
-      <c r="B103" t="s">
-        <v>180</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -4390,12 +4390,12 @@
         <v>7</v>
       </c>
       <c r="J103" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C104">
         <v>119</v>
@@ -4421,7 +4421,7 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C105">
         <v>35</v>
@@ -4447,10 +4447,10 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>182</v>
+      </c>
+      <c r="B106" t="s">
         <v>183</v>
-      </c>
-      <c r="B106" t="s">
-        <v>184</v>
       </c>
       <c r="C106">
         <v>30</v>
@@ -4474,15 +4474,15 @@
         <v>9</v>
       </c>
       <c r="J106" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>184</v>
+      </c>
+      <c r="B107" t="s">
         <v>185</v>
-      </c>
-      <c r="B107" t="s">
-        <v>186</v>
       </c>
       <c r="C107">
         <v>5</v>
@@ -4508,7 +4508,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C108">
         <v>102</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C109">
         <v>102</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C110">
         <v>102</v>
@@ -4586,7 +4586,7 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C111">
         <v>102</v>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>190</v>
+      </c>
+      <c r="B112" t="s">
         <v>191</v>
-      </c>
-      <c r="B112" t="s">
-        <v>192</v>
       </c>
       <c r="C112">
         <v>11</v>
@@ -4641,10 +4641,10 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>192</v>
+      </c>
+      <c r="B113" t="s">
         <v>193</v>
-      </c>
-      <c r="B113" t="s">
-        <v>194</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>194</v>
+      </c>
+      <c r="B114" t="s">
         <v>195</v>
-      </c>
-      <c r="B114" t="s">
-        <v>196</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -4687,10 +4687,10 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>196</v>
+      </c>
+      <c r="B115" t="s">
         <v>197</v>
-      </c>
-      <c r="B115" t="s">
-        <v>198</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -4710,10 +4710,10 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>198</v>
+      </c>
+      <c r="B116" t="s">
         <v>199</v>
-      </c>
-      <c r="B116" t="s">
-        <v>200</v>
       </c>
       <c r="C116">
         <v>6</v>
@@ -4739,10 +4739,10 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>200</v>
+      </c>
+      <c r="B117" t="s">
         <v>201</v>
-      </c>
-      <c r="B117" t="s">
-        <v>202</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -4762,10 +4762,10 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>202</v>
+      </c>
+      <c r="B118" t="s">
         <v>203</v>
-      </c>
-      <c r="B118" t="s">
-        <v>204</v>
       </c>
       <c r="C118">
         <v>6</v>
@@ -4791,7 +4791,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>205</v>
+      </c>
+      <c r="B120" t="s">
         <v>206</v>
-      </c>
-      <c r="B120" t="s">
-        <v>207</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>207</v>
+      </c>
+      <c r="B121" t="s">
         <v>208</v>
-      </c>
-      <c r="B121" t="s">
-        <v>209</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>209</v>
+      </c>
+      <c r="B122" t="s">
         <v>210</v>
-      </c>
-      <c r="B122" t="s">
-        <v>211</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -4886,10 +4886,10 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>211</v>
+      </c>
+      <c r="B123" t="s">
         <v>212</v>
-      </c>
-      <c r="B123" t="s">
-        <v>213</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>213</v>
+      </c>
+      <c r="B124" t="s">
         <v>214</v>
-      </c>
-      <c r="B124" t="s">
-        <v>215</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>215</v>
+      </c>
+      <c r="B125" t="s">
         <v>216</v>
-      </c>
-      <c r="B125" t="s">
-        <v>217</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -4955,10 +4955,10 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>217</v>
+      </c>
+      <c r="B126" t="s">
         <v>218</v>
-      </c>
-      <c r="B126" t="s">
-        <v>219</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -4978,10 +4978,10 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>219</v>
+      </c>
+      <c r="B127" t="s">
         <v>220</v>
-      </c>
-      <c r="B127" t="s">
-        <v>221</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>221</v>
+      </c>
+      <c r="B128" t="s">
         <v>222</v>
-      </c>
-      <c r="B128" t="s">
-        <v>223</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -5024,7 +5024,7 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -5035,7 +5035,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C130">
         <v>73</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>225</v>
+      </c>
+      <c r="B131" t="s">
         <v>226</v>
-      </c>
-      <c r="B131" t="s">
-        <v>227</v>
       </c>
       <c r="C131">
         <v>6</v>
@@ -5090,7 +5090,7 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -5101,7 +5101,7 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C133">
         <v>10</v>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>229</v>
+      </c>
+      <c r="B134" t="s">
         <v>230</v>
-      </c>
-      <c r="B134" t="s">
-        <v>231</v>
       </c>
       <c r="C134">
         <v>10</v>
@@ -5156,7 +5156,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C135">
         <v>56</v>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>232</v>
+      </c>
+      <c r="B136" t="s">
         <v>233</v>
-      </c>
-      <c r="B136" t="s">
-        <v>234</v>
       </c>
       <c r="C136">
         <v>6</v>
@@ -5211,10 +5211,10 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>234</v>
+      </c>
+      <c r="B137" t="s">
         <v>235</v>
-      </c>
-      <c r="B137" t="s">
-        <v>236</v>
       </c>
       <c r="C137">
         <v>6</v>
@@ -5240,10 +5240,10 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>236</v>
+      </c>
+      <c r="B138" t="s">
         <v>237</v>
-      </c>
-      <c r="B138" t="s">
-        <v>238</v>
       </c>
       <c r="C138">
         <v>6</v>
@@ -5269,10 +5269,10 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>238</v>
+      </c>
+      <c r="B139" t="s">
         <v>239</v>
-      </c>
-      <c r="B139" t="s">
-        <v>240</v>
       </c>
       <c r="C139">
         <v>22</v>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C140">
         <v>18</v>
@@ -5324,10 +5324,10 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>241</v>
+      </c>
+      <c r="B141" t="s">
         <v>242</v>
-      </c>
-      <c r="B141" t="s">
-        <v>243</v>
       </c>
       <c r="C141">
         <v>6</v>
@@ -5353,10 +5353,10 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>243</v>
+      </c>
+      <c r="B142" t="s">
         <v>244</v>
-      </c>
-      <c r="B142" t="s">
-        <v>245</v>
       </c>
       <c r="C142">
         <v>6</v>
@@ -5382,10 +5382,10 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>245</v>
+      </c>
+      <c r="B143" t="s">
         <v>246</v>
-      </c>
-      <c r="B143" t="s">
-        <v>247</v>
       </c>
       <c r="C143">
         <v>6</v>
@@ -5411,7 +5411,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C144">
         <v>6</v>
@@ -5437,10 +5437,10 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>248</v>
+      </c>
+      <c r="B145" t="s">
         <v>249</v>
-      </c>
-      <c r="B145" t="s">
-        <v>250</v>
       </c>
       <c r="C145">
         <v>6</v>
@@ -5466,7 +5466,7 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C146">
         <v>4</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>251</v>
+      </c>
+      <c r="B147" t="s">
         <v>252</v>
-      </c>
-      <c r="B147" t="s">
-        <v>253</v>
       </c>
       <c r="C147">
         <v>4</v>
@@ -5521,7 +5521,7 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C148">
         <v>6</v>
@@ -5547,10 +5547,10 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>254</v>
+      </c>
+      <c r="B149" t="s">
         <v>255</v>
-      </c>
-      <c r="B149" t="s">
-        <v>256</v>
       </c>
       <c r="C149">
         <v>6</v>
@@ -5576,7 +5576,7 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C150">
         <v>6</v>
@@ -5602,10 +5602,10 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>257</v>
+      </c>
+      <c r="B151" t="s">
         <v>258</v>
-      </c>
-      <c r="B151" t="s">
-        <v>259</v>
       </c>
       <c r="C151">
         <v>6</v>
@@ -5631,7 +5631,7 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C152">
         <v>61</v>
@@ -5657,7 +5657,7 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C153">
         <v>6</v>
@@ -5683,10 +5683,10 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>261</v>
+      </c>
+      <c r="B154" t="s">
         <v>262</v>
-      </c>
-      <c r="B154" t="s">
-        <v>263</v>
       </c>
       <c r="C154">
         <v>6</v>
@@ -5712,7 +5712,7 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C155">
         <v>61</v>
@@ -5738,10 +5738,10 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>264</v>
+      </c>
+      <c r="B156" t="s">
         <v>265</v>
-      </c>
-      <c r="B156" t="s">
-        <v>266</v>
       </c>
       <c r="C156">
         <v>11</v>
@@ -5767,10 +5767,10 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>266</v>
+      </c>
+      <c r="B157" t="s">
         <v>267</v>
-      </c>
-      <c r="B157" t="s">
-        <v>268</v>
       </c>
       <c r="C157">
         <v>6</v>
@@ -5796,10 +5796,10 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>268</v>
+      </c>
+      <c r="B158" t="s">
         <v>269</v>
-      </c>
-      <c r="B158" t="s">
-        <v>270</v>
       </c>
       <c r="C158">
         <v>11</v>
@@ -5825,10 +5825,10 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>270</v>
+      </c>
+      <c r="B159" t="s">
         <v>271</v>
-      </c>
-      <c r="B159" t="s">
-        <v>272</v>
       </c>
       <c r="C159">
         <v>6</v>
@@ -5854,10 +5854,10 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>272</v>
+      </c>
+      <c r="B160" t="s">
         <v>273</v>
-      </c>
-      <c r="B160" t="s">
-        <v>274</v>
       </c>
       <c r="C160">
         <v>2</v>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>274</v>
+      </c>
+      <c r="B161" t="s">
         <v>275</v>
-      </c>
-      <c r="B161" t="s">
-        <v>276</v>
       </c>
       <c r="C161">
         <v>6</v>
@@ -5912,10 +5912,10 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>276</v>
+      </c>
+      <c r="B162" t="s">
         <v>277</v>
-      </c>
-      <c r="B162" t="s">
-        <v>278</v>
       </c>
       <c r="C162">
         <v>3</v>
@@ -5941,7 +5941,7 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C163">
         <v>11</v>
@@ -5967,10 +5967,10 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>279</v>
+      </c>
+      <c r="B164" t="s">
         <v>280</v>
-      </c>
-      <c r="B164" t="s">
-        <v>281</v>
       </c>
       <c r="C164">
         <v>11</v>
@@ -5996,7 +5996,7 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C165">
         <v>54</v>
@@ -6022,7 +6022,7 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C166">
         <v>54</v>
@@ -6048,10 +6048,10 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>282</v>
+      </c>
+      <c r="B167" t="s">
         <v>283</v>
-      </c>
-      <c r="B167" t="s">
-        <v>284</v>
       </c>
       <c r="C167">
         <v>11</v>
@@ -6077,10 +6077,10 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>284</v>
+      </c>
+      <c r="B168" t="s">
         <v>285</v>
-      </c>
-      <c r="B168" t="s">
-        <v>286</v>
       </c>
       <c r="C168">
         <v>6</v>
@@ -6106,10 +6106,10 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
+        <v>286</v>
+      </c>
+      <c r="B169" t="s">
         <v>287</v>
-      </c>
-      <c r="B169" t="s">
-        <v>288</v>
       </c>
       <c r="C169">
         <v>6</v>
@@ -6135,10 +6135,10 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>288</v>
+      </c>
+      <c r="B170" t="s">
         <v>289</v>
-      </c>
-      <c r="B170" t="s">
-        <v>290</v>
       </c>
       <c r="C170">
         <v>6</v>
@@ -6164,10 +6164,10 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
+        <v>290</v>
+      </c>
+      <c r="B171" t="s">
         <v>291</v>
-      </c>
-      <c r="B171" t="s">
-        <v>292</v>
       </c>
       <c r="C171">
         <v>6</v>
@@ -6193,10 +6193,10 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>292</v>
+      </c>
+      <c r="B172" t="s">
         <v>293</v>
-      </c>
-      <c r="B172" t="s">
-        <v>294</v>
       </c>
       <c r="C172">
         <v>6</v>
@@ -6222,10 +6222,10 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>294</v>
+      </c>
+      <c r="B173" t="s">
         <v>295</v>
-      </c>
-      <c r="B173" t="s">
-        <v>296</v>
       </c>
       <c r="C173">
         <v>6</v>
@@ -6251,10 +6251,10 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>296</v>
+      </c>
+      <c r="B174" t="s">
         <v>297</v>
-      </c>
-      <c r="B174" t="s">
-        <v>298</v>
       </c>
       <c r="C174">
         <v>6</v>
@@ -6280,7 +6280,7 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C175">
         <v>20</v>
@@ -6306,10 +6306,10 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>298</v>
+      </c>
+      <c r="B176" t="s">
         <v>299</v>
-      </c>
-      <c r="B176" t="s">
-        <v>300</v>
       </c>
       <c r="C176">
         <v>4</v>
@@ -6335,10 +6335,10 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>300</v>
+      </c>
+      <c r="B177" t="s">
         <v>301</v>
-      </c>
-      <c r="B177" t="s">
-        <v>302</v>
       </c>
       <c r="C177">
         <v>4</v>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>302</v>
+      </c>
+      <c r="B178" t="s">
         <v>303</v>
-      </c>
-      <c r="B178" t="s">
-        <v>304</v>
       </c>
       <c r="C178">
         <v>4</v>
@@ -6393,10 +6393,10 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>304</v>
+      </c>
+      <c r="B179" t="s">
         <v>305</v>
-      </c>
-      <c r="B179" t="s">
-        <v>306</v>
       </c>
       <c r="C179">
         <v>4</v>
@@ -6422,10 +6422,10 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>306</v>
+      </c>
+      <c r="B180" t="s">
         <v>307</v>
-      </c>
-      <c r="B180" t="s">
-        <v>308</v>
       </c>
       <c r="C180">
         <v>4</v>
@@ -6451,10 +6451,10 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>308</v>
+      </c>
+      <c r="B181" t="s">
         <v>309</v>
-      </c>
-      <c r="B181" t="s">
-        <v>310</v>
       </c>
       <c r="C181">
         <v>11</v>
@@ -6480,7 +6480,7 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C182">
         <v>49</v>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C183">
         <v>49</v>
@@ -6532,10 +6532,10 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
+        <v>311</v>
+      </c>
+      <c r="B184" t="s">
         <v>312</v>
-      </c>
-      <c r="B184" t="s">
-        <v>313</v>
       </c>
       <c r="C184">
         <v>11</v>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
+        <v>313</v>
+      </c>
+      <c r="B185" t="s">
         <v>314</v>
-      </c>
-      <c r="B185" t="s">
-        <v>315</v>
       </c>
       <c r="C185">
         <v>6</v>
@@ -6590,10 +6590,10 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
+        <v>315</v>
+      </c>
+      <c r="B186" t="s">
         <v>316</v>
-      </c>
-      <c r="B186" t="s">
-        <v>317</v>
       </c>
       <c r="C186">
         <v>4</v>
@@ -6619,10 +6619,10 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>317</v>
+      </c>
+      <c r="B187" t="s">
         <v>318</v>
-      </c>
-      <c r="B187" t="s">
-        <v>319</v>
       </c>
       <c r="C187">
         <v>6</v>
@@ -6648,10 +6648,10 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>319</v>
+      </c>
+      <c r="B188" t="s">
         <v>320</v>
-      </c>
-      <c r="B188" t="s">
-        <v>321</v>
       </c>
       <c r="C188">
         <v>11</v>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>321</v>
+      </c>
+      <c r="B189" t="s">
         <v>322</v>
-      </c>
-      <c r="B189" t="s">
-        <v>323</v>
       </c>
       <c r="C189">
         <v>4</v>
@@ -6706,10 +6706,10 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>323</v>
+      </c>
+      <c r="B190" t="s">
         <v>324</v>
-      </c>
-      <c r="B190" t="s">
-        <v>325</v>
       </c>
       <c r="C190">
         <v>11</v>
@@ -6735,7 +6735,7 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C191">
         <v>23</v>
@@ -6761,10 +6761,10 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>325</v>
+      </c>
+      <c r="B192" t="s">
         <v>326</v>
-      </c>
-      <c r="B192" t="s">
-        <v>327</v>
       </c>
       <c r="C192">
         <v>6</v>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>327</v>
+      </c>
+      <c r="B193" t="s">
         <v>328</v>
-      </c>
-      <c r="B193" t="s">
-        <v>329</v>
       </c>
       <c r="C193">
         <v>6</v>
@@ -6819,10 +6819,10 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>329</v>
+      </c>
+      <c r="B194" t="s">
         <v>330</v>
-      </c>
-      <c r="B194" t="s">
-        <v>331</v>
       </c>
       <c r="C194">
         <v>6</v>
@@ -6848,7 +6848,7 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C195">
         <v>22</v>
@@ -6874,10 +6874,10 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>332</v>
+      </c>
+      <c r="B196" t="s">
         <v>333</v>
-      </c>
-      <c r="B196" t="s">
-        <v>334</v>
       </c>
       <c r="C196">
         <v>11</v>
@@ -6903,10 +6903,10 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>334</v>
+      </c>
+      <c r="B197" t="s">
         <v>335</v>
-      </c>
-      <c r="B197" t="s">
-        <v>336</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -6926,10 +6926,10 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>336</v>
+      </c>
+      <c r="B198" t="s">
         <v>337</v>
-      </c>
-      <c r="B198" t="s">
-        <v>338</v>
       </c>
       <c r="C198">
         <v>11</v>
@@ -6955,10 +6955,10 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>338</v>
+      </c>
+      <c r="B199" t="s">
         <v>339</v>
-      </c>
-      <c r="B199" t="s">
-        <v>340</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -6984,7 +6984,7 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C200">
         <v>102</v>
@@ -7010,7 +7010,7 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C201">
         <v>22</v>
@@ -7036,10 +7036,10 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>342</v>
+      </c>
+      <c r="B202" t="s">
         <v>343</v>
-      </c>
-      <c r="B202" t="s">
-        <v>344</v>
       </c>
       <c r="C202">
         <v>22</v>
@@ -7065,7 +7065,7 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C203">
         <v>44</v>
@@ -7091,10 +7091,10 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
+        <v>345</v>
+      </c>
+      <c r="B204" t="s">
         <v>346</v>
-      </c>
-      <c r="B204" t="s">
-        <v>347</v>
       </c>
       <c r="C204">
         <v>17</v>
@@ -7120,10 +7120,10 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
+        <v>347</v>
+      </c>
+      <c r="B205" t="s">
         <v>348</v>
-      </c>
-      <c r="B205" t="s">
-        <v>349</v>
       </c>
       <c r="C205">
         <v>5</v>
@@ -7149,10 +7149,10 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
+        <v>349</v>
+      </c>
+      <c r="B206" t="s">
         <v>350</v>
-      </c>
-      <c r="B206" t="s">
-        <v>351</v>
       </c>
       <c r="C206">
         <v>44</v>
@@ -7178,7 +7178,7 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C207">
         <v>66</v>
@@ -7204,7 +7204,7 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C208">
         <v>37</v>
@@ -7230,10 +7230,10 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B209" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C209">
         <v>22</v>
@@ -7259,10 +7259,10 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>354</v>
+      </c>
+      <c r="B210" t="s">
         <v>355</v>
-      </c>
-      <c r="B210" t="s">
-        <v>356</v>
       </c>
       <c r="C210">
         <v>6</v>
@@ -7288,7 +7288,7 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C211">
         <v>11</v>
@@ -7314,10 +7314,10 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>357</v>
+      </c>
+      <c r="B212" t="s">
         <v>358</v>
-      </c>
-      <c r="B212" t="s">
-        <v>359</v>
       </c>
       <c r="C212">
         <v>6</v>
@@ -7343,10 +7343,10 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>359</v>
+      </c>
+      <c r="B213" t="s">
         <v>360</v>
-      </c>
-      <c r="B213" t="s">
-        <v>361</v>
       </c>
       <c r="C213">
         <v>5</v>
@@ -7372,7 +7372,7 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C214">
         <v>11</v>
@@ -7398,10 +7398,10 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>362</v>
+      </c>
+      <c r="B215" t="s">
         <v>363</v>
-      </c>
-      <c r="B215" t="s">
-        <v>364</v>
       </c>
       <c r="C215">
         <v>11</v>
@@ -7427,7 +7427,7 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C216">
         <v>27</v>
@@ -7453,10 +7453,10 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>365</v>
+      </c>
+      <c r="B217" t="s">
         <v>366</v>
-      </c>
-      <c r="B217" t="s">
-        <v>367</v>
       </c>
       <c r="C217">
         <v>11</v>
@@ -7482,10 +7482,10 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>367</v>
+      </c>
+      <c r="B218" t="s">
         <v>368</v>
-      </c>
-      <c r="B218" t="s">
-        <v>369</v>
       </c>
       <c r="C218">
         <v>5</v>
@@ -7511,10 +7511,10 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
+        <v>369</v>
+      </c>
+      <c r="B219" t="s">
         <v>370</v>
-      </c>
-      <c r="B219" t="s">
-        <v>371</v>
       </c>
       <c r="C219">
         <v>22</v>
@@ -7540,7 +7540,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C220">
         <v>15</v>
@@ -7566,10 +7566,10 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
+        <v>372</v>
+      </c>
+      <c r="B221" t="s">
         <v>373</v>
-      </c>
-      <c r="B221" t="s">
-        <v>374</v>
       </c>
       <c r="C221">
         <v>5</v>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
+        <v>374</v>
+      </c>
+      <c r="B222" t="s">
         <v>375</v>
-      </c>
-      <c r="B222" t="s">
-        <v>376</v>
       </c>
       <c r="C222">
         <v>10</v>
@@ -7624,7 +7624,7 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C223">
         <v>16</v>
@@ -7650,10 +7650,10 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
+        <v>377</v>
+      </c>
+      <c r="B224" t="s">
         <v>378</v>
-      </c>
-      <c r="B224" t="s">
-        <v>379</v>
       </c>
       <c r="C224">
         <v>11</v>
@@ -7679,10 +7679,10 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
+        <v>379</v>
+      </c>
+      <c r="B225" t="s">
         <v>380</v>
-      </c>
-      <c r="B225" t="s">
-        <v>381</v>
       </c>
       <c r="C225">
         <v>5</v>
@@ -7708,7 +7708,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C226">
         <v>33</v>
@@ -7734,10 +7734,10 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>382</v>
+      </c>
+      <c r="B227" t="s">
         <v>383</v>
-      </c>
-      <c r="B227" t="s">
-        <v>384</v>
       </c>
       <c r="C227">
         <v>28</v>
@@ -7763,10 +7763,10 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
+        <v>384</v>
+      </c>
+      <c r="B228" t="s">
         <v>385</v>
-      </c>
-      <c r="B228" t="s">
-        <v>386</v>
       </c>
       <c r="C228">
         <v>5</v>
@@ -7792,10 +7792,10 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
+        <v>386</v>
+      </c>
+      <c r="B229" t="s">
         <v>387</v>
-      </c>
-      <c r="B229" t="s">
-        <v>388</v>
       </c>
       <c r="C229">
         <v>28</v>
@@ -7821,7 +7821,7 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C230">
         <v>110</v>
@@ -7847,7 +7847,7 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C231">
         <v>106</v>
@@ -7873,10 +7873,10 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>390</v>
+      </c>
+      <c r="B232" t="s">
         <v>391</v>
-      </c>
-      <c r="B232" t="s">
-        <v>392</v>
       </c>
       <c r="C232">
         <v>20</v>
@@ -7902,10 +7902,10 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
+        <v>392</v>
+      </c>
+      <c r="B233" t="s">
         <v>393</v>
-      </c>
-      <c r="B233" t="s">
-        <v>394</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -7925,10 +7925,10 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
+        <v>394</v>
+      </c>
+      <c r="B234" t="s">
         <v>395</v>
-      </c>
-      <c r="B234" t="s">
-        <v>396</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -7948,10 +7948,10 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
+        <v>396</v>
+      </c>
+      <c r="B235" t="s">
         <v>397</v>
-      </c>
-      <c r="B235" t="s">
-        <v>398</v>
       </c>
       <c r="C235">
         <v>6</v>
@@ -7977,7 +7977,7 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C236">
         <v>80</v>
@@ -8003,7 +8003,7 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C237">
         <v>30</v>
@@ -8029,10 +8029,10 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
+        <v>400</v>
+      </c>
+      <c r="B238" t="s">
         <v>401</v>
-      </c>
-      <c r="B238" t="s">
-        <v>402</v>
       </c>
       <c r="C238">
         <v>30</v>
@@ -8058,7 +8058,7 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C239">
         <v>45</v>
@@ -8084,10 +8084,10 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
+        <v>403</v>
+      </c>
+      <c r="B240" t="s">
         <v>404</v>
-      </c>
-      <c r="B240" t="s">
-        <v>405</v>
       </c>
       <c r="C240">
         <v>10</v>
@@ -8113,10 +8113,10 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
+        <v>405</v>
+      </c>
+      <c r="B241" t="s">
         <v>406</v>
-      </c>
-      <c r="B241" t="s">
-        <v>407</v>
       </c>
       <c r="C241">
         <v>6</v>
@@ -8142,10 +8142,10 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>407</v>
+      </c>
+      <c r="B242" t="s">
         <v>408</v>
-      </c>
-      <c r="B242" t="s">
-        <v>409</v>
       </c>
       <c r="C242">
         <v>6</v>
@@ -8171,10 +8171,10 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
+        <v>409</v>
+      </c>
+      <c r="B243" t="s">
         <v>410</v>
-      </c>
-      <c r="B243" t="s">
-        <v>411</v>
       </c>
       <c r="C243">
         <v>6</v>
@@ -8200,10 +8200,10 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>411</v>
+      </c>
+      <c r="B244" t="s">
         <v>412</v>
-      </c>
-      <c r="B244" t="s">
-        <v>413</v>
       </c>
       <c r="C244">
         <v>17</v>
@@ -8229,7 +8229,7 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C245">
         <v>0</v>
@@ -8240,7 +8240,7 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -8251,7 +8251,7 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C247">
         <v>0</v>
@@ -8262,7 +8262,7 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C248">
         <v>0</v>
@@ -8273,7 +8273,7 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -8284,7 +8284,7 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C250">
         <v>2</v>
@@ -8310,10 +8310,10 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
+        <v>419</v>
+      </c>
+      <c r="B251" t="s">
         <v>420</v>
-      </c>
-      <c r="B251" t="s">
-        <v>421</v>
       </c>
       <c r="C251">
         <v>2</v>
@@ -8339,7 +8339,7 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C252">
         <v>35</v>
@@ -8365,7 +8365,7 @@
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C253">
         <v>30</v>
@@ -8391,10 +8391,10 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
+        <v>423</v>
+      </c>
+      <c r="B254" t="s">
         <v>424</v>
-      </c>
-      <c r="B254" t="s">
-        <v>425</v>
       </c>
       <c r="C254">
         <v>0</v>
@@ -8414,10 +8414,10 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
+        <v>425</v>
+      </c>
+      <c r="B255" t="s">
         <v>426</v>
-      </c>
-      <c r="B255" t="s">
-        <v>427</v>
       </c>
       <c r="C255">
         <v>0</v>
@@ -8437,10 +8437,10 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
+        <v>427</v>
+      </c>
+      <c r="B256" t="s">
         <v>428</v>
-      </c>
-      <c r="B256" t="s">
-        <v>429</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -8460,10 +8460,10 @@
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
+        <v>429</v>
+      </c>
+      <c r="B257" t="s">
         <v>430</v>
-      </c>
-      <c r="B257" t="s">
-        <v>431</v>
       </c>
       <c r="C257">
         <v>0</v>
@@ -8483,10 +8483,10 @@
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
+        <v>431</v>
+      </c>
+      <c r="B258" t="s">
         <v>432</v>
-      </c>
-      <c r="B258" t="s">
-        <v>433</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -8506,7 +8506,7 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C259">
         <v>35</v>
@@ -8532,10 +8532,10 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
+        <v>434</v>
+      </c>
+      <c r="B260" t="s">
         <v>435</v>
-      </c>
-      <c r="B260" t="s">
-        <v>436</v>
       </c>
       <c r="C260">
         <v>5</v>
@@ -8561,10 +8561,10 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
+        <v>436</v>
+      </c>
+      <c r="B261" t="s">
         <v>437</v>
-      </c>
-      <c r="B261" t="s">
-        <v>438</v>
       </c>
       <c r="C261">
         <v>5</v>
@@ -8590,10 +8590,10 @@
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
+        <v>438</v>
+      </c>
+      <c r="B262" t="s">
         <v>439</v>
-      </c>
-      <c r="B262" t="s">
-        <v>440</v>
       </c>
       <c r="C262">
         <v>5</v>
@@ -8619,10 +8619,10 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
+        <v>440</v>
+      </c>
+      <c r="B263" t="s">
         <v>441</v>
-      </c>
-      <c r="B263" t="s">
-        <v>442</v>
       </c>
       <c r="C263">
         <v>5</v>
@@ -8648,10 +8648,10 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
+        <v>442</v>
+      </c>
+      <c r="B264" t="s">
         <v>443</v>
-      </c>
-      <c r="B264" t="s">
-        <v>444</v>
       </c>
       <c r="C264">
         <v>5</v>
@@ -8677,7 +8677,7 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C265">
         <v>97</v>
@@ -8703,7 +8703,7 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C266">
         <v>97</v>
@@ -8729,7 +8729,7 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C267">
         <v>48</v>
@@ -8755,10 +8755,10 @@
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>447</v>
+      </c>
+      <c r="B268" t="s">
         <v>448</v>
-      </c>
-      <c r="B268" t="s">
-        <v>449</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -8784,10 +8784,10 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
+        <v>449</v>
+      </c>
+      <c r="B269" t="s">
         <v>450</v>
-      </c>
-      <c r="B269" t="s">
-        <v>451</v>
       </c>
       <c r="C269">
         <v>5</v>
@@ -8813,10 +8813,10 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
+        <v>451</v>
+      </c>
+      <c r="B270" t="s">
         <v>452</v>
-      </c>
-      <c r="B270" t="s">
-        <v>453</v>
       </c>
       <c r="C270">
         <v>4</v>
@@ -8842,10 +8842,10 @@
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B271" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C271">
         <v>2</v>
@@ -8871,10 +8871,10 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
+        <v>454</v>
+      </c>
+      <c r="B272" t="s">
         <v>455</v>
-      </c>
-      <c r="B272" t="s">
-        <v>456</v>
       </c>
       <c r="C272">
         <v>2</v>
@@ -8900,10 +8900,10 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
+        <v>456</v>
+      </c>
+      <c r="B273" t="s">
         <v>457</v>
-      </c>
-      <c r="B273" t="s">
-        <v>458</v>
       </c>
       <c r="C273">
         <v>2</v>
@@ -8929,10 +8929,10 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
+        <v>458</v>
+      </c>
+      <c r="B274" t="s">
         <v>459</v>
-      </c>
-      <c r="B274" t="s">
-        <v>460</v>
       </c>
       <c r="C274">
         <v>5</v>
@@ -8958,10 +8958,10 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
+        <v>460</v>
+      </c>
+      <c r="B275" t="s">
         <v>461</v>
-      </c>
-      <c r="B275" t="s">
-        <v>462</v>
       </c>
       <c r="C275">
         <v>20</v>
@@ -8987,10 +8987,10 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
+        <v>462</v>
+      </c>
+      <c r="B276" t="s">
         <v>463</v>
-      </c>
-      <c r="B276" t="s">
-        <v>464</v>
       </c>
       <c r="C276">
         <v>6</v>
@@ -9016,10 +9016,10 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
+        <v>464</v>
+      </c>
+      <c r="B277" t="s">
         <v>465</v>
-      </c>
-      <c r="B277" t="s">
-        <v>466</v>
       </c>
       <c r="C277">
         <v>5</v>
@@ -9045,10 +9045,10 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
+        <v>466</v>
+      </c>
+      <c r="B278" t="s">
         <v>467</v>
-      </c>
-      <c r="B278" t="s">
-        <v>468</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -9074,10 +9074,10 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
+        <v>468</v>
+      </c>
+      <c r="B279" t="s">
         <v>469</v>
-      </c>
-      <c r="B279" t="s">
-        <v>470</v>
       </c>
       <c r="C279">
         <v>6</v>
@@ -9103,10 +9103,10 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
+        <v>470</v>
+      </c>
+      <c r="B280" t="s">
         <v>471</v>
-      </c>
-      <c r="B280" t="s">
-        <v>472</v>
       </c>
       <c r="C280">
         <v>3</v>
@@ -9132,7 +9132,7 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C281">
         <v>69</v>
@@ -9158,10 +9158,10 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
+        <v>473</v>
+      </c>
+      <c r="B282" t="s">
         <v>474</v>
-      </c>
-      <c r="B282" t="s">
-        <v>475</v>
       </c>
       <c r="C282">
         <v>3</v>
@@ -9187,10 +9187,10 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
+        <v>475</v>
+      </c>
+      <c r="B283" t="s">
         <v>476</v>
-      </c>
-      <c r="B283" t="s">
-        <v>477</v>
       </c>
       <c r="C283">
         <v>3</v>
@@ -9216,10 +9216,10 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
+        <v>477</v>
+      </c>
+      <c r="B284" t="s">
         <v>478</v>
-      </c>
-      <c r="B284" t="s">
-        <v>479</v>
       </c>
       <c r="C284">
         <v>4</v>
@@ -9245,10 +9245,10 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
+        <v>479</v>
+      </c>
+      <c r="B285" t="s">
         <v>480</v>
-      </c>
-      <c r="B285" t="s">
-        <v>481</v>
       </c>
       <c r="C285">
         <v>11</v>
@@ -9274,10 +9274,10 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
+        <v>481</v>
+      </c>
+      <c r="B286" t="s">
         <v>482</v>
-      </c>
-      <c r="B286" t="s">
-        <v>483</v>
       </c>
       <c r="C286">
         <v>4</v>
@@ -9303,10 +9303,10 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
+        <v>483</v>
+      </c>
+      <c r="B287" t="s">
         <v>484</v>
-      </c>
-      <c r="B287" t="s">
-        <v>485</v>
       </c>
       <c r="C287">
         <v>14</v>
@@ -9332,10 +9332,10 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
+        <v>485</v>
+      </c>
+      <c r="B288" t="s">
         <v>486</v>
-      </c>
-      <c r="B288" t="s">
-        <v>487</v>
       </c>
       <c r="C288">
         <v>5</v>
@@ -9361,10 +9361,10 @@
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
+        <v>487</v>
+      </c>
+      <c r="B289" t="s">
         <v>488</v>
-      </c>
-      <c r="B289" t="s">
-        <v>489</v>
       </c>
       <c r="C289">
         <v>20</v>
@@ -9390,10 +9390,10 @@
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
+        <v>489</v>
+      </c>
+      <c r="B290" t="s">
         <v>490</v>
-      </c>
-      <c r="B290" t="s">
-        <v>491</v>
       </c>
       <c r="C290">
         <v>2</v>
@@ -9419,10 +9419,10 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
+        <v>491</v>
+      </c>
+      <c r="B291" t="s">
         <v>492</v>
-      </c>
-      <c r="B291" t="s">
-        <v>493</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -9448,10 +9448,10 @@
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
+        <v>493</v>
+      </c>
+      <c r="B292" t="s">
         <v>494</v>
-      </c>
-      <c r="B292" t="s">
-        <v>495</v>
       </c>
       <c r="C292">
         <v>10</v>
@@ -9477,7 +9477,7 @@
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C293">
         <v>0</v>
@@ -9488,7 +9488,7 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -9499,7 +9499,7 @@
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C295">
         <v>0</v>
@@ -9510,7 +9510,7 @@
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C296">
         <v>0</v>
@@ -9521,7 +9521,7 @@
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C297">
         <v>0</v>
@@ -9532,7 +9532,7 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C298">
         <v>0</v>
@@ -9543,7 +9543,7 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C299">
         <v>0</v>
@@ -9554,7 +9554,7 @@
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C300">
         <v>0</v>
@@ -9565,7 +9565,7 @@
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C301">
         <v>0</v>
@@ -9576,7 +9576,7 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -9587,7 +9587,7 @@
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -9598,7 +9598,7 @@
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -9609,7 +9609,7 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -9620,7 +9620,7 @@
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C306">
         <v>0</v>
@@ -9631,7 +9631,7 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -9642,7 +9642,7 @@
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -9653,7 +9653,7 @@
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -9664,7 +9664,7 @@
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -9675,7 +9675,7 @@
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -9686,7 +9686,7 @@
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C312">
         <v>0</v>
@@ -9697,7 +9697,7 @@
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -9708,7 +9708,7 @@
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C314">
         <v>0</v>
@@ -9719,7 +9719,7 @@
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C315">
         <v>0</v>
@@ -9730,7 +9730,7 @@
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C316">
         <v>0</v>
@@ -9741,7 +9741,7 @@
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -9752,7 +9752,7 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -9763,7 +9763,7 @@
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -9774,7 +9774,7 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -9785,7 +9785,7 @@
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -9796,7 +9796,7 @@
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C322">
         <v>0</v>
@@ -9807,7 +9807,7 @@
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C323">
         <v>0</v>
@@ -9818,7 +9818,7 @@
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -9829,7 +9829,7 @@
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C325">
         <v>0</v>
@@ -9840,7 +9840,7 @@
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -9851,7 +9851,7 @@
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -9862,7 +9862,7 @@
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C328">
         <v>0</v>
@@ -9873,7 +9873,7 @@
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C329">
         <v>0</v>
@@ -9884,7 +9884,7 @@
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C330">
         <v>0</v>
@@ -9895,7 +9895,7 @@
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C331">
         <v>0</v>
@@ -9906,7 +9906,7 @@
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C332">
         <v>0</v>
@@ -9917,7 +9917,7 @@
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C333">
         <v>0</v>
@@ -9928,7 +9928,7 @@
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C334">
         <v>0</v>
@@ -9939,7 +9939,7 @@
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C335">
         <v>0</v>
@@ -9950,7 +9950,7 @@
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C336">
         <v>0</v>
@@ -9961,7 +9961,7 @@
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C337">
         <v>0</v>
@@ -9972,7 +9972,7 @@
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C338">
         <v>0</v>
@@ -9983,7 +9983,7 @@
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C339">
         <v>0</v>
@@ -9994,7 +9994,7 @@
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C340">
         <v>0</v>
@@ -10005,7 +10005,7 @@
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C341">
         <v>0</v>
@@ -10016,7 +10016,7 @@
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C342">
         <v>0</v>

--- a/data/CL31.xlsx
+++ b/data/CL31.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adane\dm_tracker\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8906824D-A6D3-4D93-A329-E83E370578E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4853F291-DEE9-4022-BFF0-6EAAD88EC495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7BD6478B-385B-46E3-99A0-A28036FEB319}"/>
   </bookViews>
